--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Wixom, MI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>DevOps Engineer - Wixom, MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Redzara LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Sr Data Modeler</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,81 +1672,81 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,199 +2036,199 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer, Sales Data Domain (Remote)</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,242 +2386,242 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052ff42df262f3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineer, Sales Data Domain (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior BI Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>Herc Rentals</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
+          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,682 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II - AI Research</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Collaboration.Ai</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Solutions Engineer, West Coast</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Innovative Systems</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Azure Security Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Quality Analyst - 5821</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Advanced Systems Design</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Montgomery, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Fiduciary Tech</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Envestnet</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Full Stack Java Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -1798,35 +1798,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3c7c8412ad1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Software Engineer II, Ads Delivery</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Raptive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, DynamoDB, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e82c7cbfd626d992</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Envestnet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Envestnet</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>The RealReal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Redzara LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Modeler</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Redzara LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Sr Data Modeler</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II, Ads Delivery</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Raptive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, DynamoDB, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82c7cbfd626d992</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Software Engineer II, Ads Delivery</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Raptive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, DynamoDB, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e82c7cbfd626d992</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Sales Data Domain (Remote)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior BI Data Scientist</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Herc Rentals</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bonita Springs, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior BI Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Herc Rentals</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,15 +3138,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Quality Analyst - 5821</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Advanced Systems Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Data Quality Analyst - 5821</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>Advanced Systems Design</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Envestnet</t>
+          <t>Fiduciary Tech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Citco</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Envestnet</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,85 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full Stack Java Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>GLIDER.ai</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>The RealReal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Redzara LLC</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Modeler</t>
+          <t>ServiceNow Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>Redzara LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
+          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Sr Data Modeler</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
         </is>
       </c>
     </row>
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior BI Data Scientist</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Herc Rentals</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bonita Springs, FL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior BI Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Herc Rentals</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Quality Analyst - 5821</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Advanced Systems Design</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Quality Analyst - 5821</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>Advanced Systems Design</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
+          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Citco</t>
+          <t>Fiduciary Tech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
+          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Envestnet</t>
+          <t>Citco</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Envestnet</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,15 +3881,85 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Talent Kloud</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d77e5d93503e970</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full Stack Java Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,60 +1518,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ServiceNow Consultant</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Redzara LLC</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edc3ae2890245d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Modeler</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, Tableau, MLOps, MLflow, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II, Ads Delivery</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Raptive</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, DynamoDB, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82c7cbfd626d992</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior BI Data Scientist</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Herc Rentals</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bonita Springs, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, ETL, MLOps, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada483ee6dc6f16f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Quality Analyst - 5821</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Advanced Systems Design</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f705802002c673cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,357 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06d71fd9191f34</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Citco</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a22f4af2bc60f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Platform Engineer II</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Envestnet</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ebbef85373bda7</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af7b83e4a56167a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>.NET Architect</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Talent Kloud</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d77e5d93503e970</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Full Stack Java Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Southlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,87 +713,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Wixom, MI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>DevOps Engineer - Wixom, MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLIDER.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
+          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>GLIDER.ai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,104 +2621,104 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,15 +3601,120 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>.NET Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>The RealReal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,77 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>.NET Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19e37e48078f59f2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,42 +3156,42 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,120 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,87 +3181,87 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,15 +3741,85 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>DocMe360</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b261e4efaa78a896</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>DocMe360</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b324a9abb3a15c5b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>A.I. Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Mindset Care, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer — Public Safety Cloud Integrations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca08f99f806234c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,155 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DocMe360</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b261e4efaa78a896</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocMe360</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324a9abb3a15c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,42 +1931,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Databricks, Scala, Kafka, SQL Server, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer — Public Safety Cloud Integrations</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca08f99f806234c</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce221f86292702dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Snowflake, Oracle, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,225 +3741,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Wixom, MI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>DevOps Engineer - Wixom, MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95627fd021d5b3c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
         </is>
       </c>
     </row>
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GLIDER.ai</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41dc227e9577793</t>
+          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLIDER.ai</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>The RealReal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b67afc52d547a</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16aa76cee6df9592</t>
+          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Flume, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298206a805e9200a</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
@@ -1868,70 +1868,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Zookeeper, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e20032bf66a0bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,104 +2656,104 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,42 +3156,42 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Collaboration.Ai</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, NoSQL, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03aa36a9575000b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c0de1886689777</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,122 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed0702643990e72</t>
+          <t>https://www.indeed.com/viewjob?jk=cb173fd010bc37d5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Specialist Software Engineering - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West Lake, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d2af5d54195fff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec5847773fc77b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Onsite Interviews (Denver)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb173fd010bc37d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6cdd88a05bdf3bdd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - Onsite Interviews (Denver)</t>
+          <t>Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Kennesaw State University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec5847773fc77b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cdd88a05bdf3bdd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kennesaw State University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>DevOps Engineer - Wixom, MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Wixom, MI</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>GLIDER.ai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25df4c9eb71eaf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLIDER.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Salesforce Financial Services Cloud Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,77 +2656,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,94 +2736,94 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, MySQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,42 +3261,42 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer — AWS, Observability &amp; Security</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Collaboration.Ai</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c23fa1db266892</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Application Architect - Amazon Connect SME</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=16ff12a5782403e3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Entry Level Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Computershare</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,155 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GLIDER.ai</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d674d73add7909a</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Coughlan Companies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>North Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,104 +1816,104 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Salesforce Financial Services Cloud Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Salesforce Financial Services Cloud Consultant</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,77 +2236,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,104 +2726,104 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,112 +3181,112 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Application Architect - Amazon Connect SME</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=16ff12a5782403e3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>Entry Level Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Application Architect - Amazon Connect SME</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Computershare</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
+          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ff12a5782403e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,225 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,95 +573,95 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kennesaw State University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Medallion Architecture, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab4ea66cd88f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Scientist I &amp; II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,119 +776,119 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99039fae76a8a71c</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Wixom, MI</t>
+          <t>SAP APME Architect (Agent Performance Management)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Emcube Technlogy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2872b9dd886ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-Level Systems Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>Computer Magic, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Monona, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=69ebbeeceb66ec13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,28 +902,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,172 +986,172 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coughlan Companies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Mankato, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bb96a90f33b0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Jockey Club</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>AI Solution Architect - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,94 +1756,94 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
         </is>
       </c>
     </row>
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Salesforce Financial Services Cloud Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Salesforce Financial Services Cloud Consultant</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,139 +2621,139 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Solutions Engineer, West Coast</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaca1c6c853922d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,15 +3068,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,84 +3086,84 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65264a65d2d0171c</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>AI/ML - Applied AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, Power BI, Tableau, DataOps, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=d0106965447754c2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,365 +3216,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Salesforce AI / Einstein Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Application Architect - Amazon Connect SME</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16ff12a5782403e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1d06ec90d0b551f</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Dask, PostgreSQL, MongoDB, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Computershare</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, Oracle, SQL Server, Jenkins, Azure DevOps, Maven, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dce722905ce4a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,87 +573,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist I &amp; II</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist I &amp; II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP APME Architect (Agent Performance Management)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emcube Technlogy</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entry-Level Systems Administrator</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Computer Magic, Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monona, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,112 +836,112 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ebbeeceb66ec13</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>SAP APME Architect (Agent Performance Management)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Emcube Technlogy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Entry-Level Systems Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Computer Magic, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Monona, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=69ebbeeceb66ec13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8fa6b85043976ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9936790641cf055b</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Jockey Club</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2850dd5426ab2ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Remote</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>AI Solution Architect - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea5f9d3c3f649976</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeea819f2acfdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1566055ee1ec333e</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70eb247460f670c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Platform Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f3614925fa0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,77 +2096,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Salesforce Financial Services Cloud Consultant</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49aab47ecac4bb84</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22a108bf442eae</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecd7c928d93b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc65fbd4cd51c459</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Sundt</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c6b8d6d31caa29</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,24 +2446,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Snowflake, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7b707e648dec2</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,129 +2876,129 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer, West Coast</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Snowflake, ETL, ELT, dbt, DataOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abaa82c9cef998c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=07073f5e67bf6929</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nexxen</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1c6fb0f0eba666</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI/ML - Applied AI Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Power BI, Tableau, DataOps, MLOps, CI/CD, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0106965447754c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,85 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,60 +748,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PHP Web Application Developer (Modernization)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>EBG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f42f3c1cc306e46b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>PHP Web Application Developer (Modernization)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>EBG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8d17ef03868a4db</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>PHP Web Application Developer (Modernization)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>EBG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c2f5b1a7f332d1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP APME Architect (Agent Performance Management)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emcube Technlogy</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Entry-Level Systems Administrator</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Computer Magic, Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monona, WI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ebbeeceb66ec13</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>SAP APME Architect (Agent Performance Management)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Emcube Technlogy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,38 +1042,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Polars, SQL Server, ETL</t>
+          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>DocMe360</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=b261e4efaa78a896</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocMe360</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b324a9abb3a15c5b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,112 +1536,112 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Sr Data Modeler</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Popular, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=c2653ae0372ac3e8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solution Architect - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,147 +2096,147 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sundt</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbd92abd04640aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,147 +2481,147 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Integrations and Implementation</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,42 +2666,42 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=d903df923be7974b</t>
         </is>
       </c>
     </row>
@@ -2713,20 +2713,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,94 +2736,94 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07073f5e67bf6929</t>
+          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1c6fb0f0eba666</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,77 +3226,672 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr Python Developer - Onsite - Atlanta GA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>The Clearing House Payments Company</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Liberty, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gong</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II - AI Research</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II - AI Research</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II - AI Research</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>The New IEM, LLC</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07073f5e67bf6929</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nexxen</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e1c6fb0f0eba666</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Salesforce AI / Einstein Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Inland Empire Health Plan</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D98" t="n">
         <v>10.4</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full Stack Java Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-24.xlsx
+++ b/results/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Onsite Interviews (Denver)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,207 +496,207 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb173fd010bc37d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6cdd88a05bdf3bdd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - Onsite Interviews (Denver)</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec5847773fc77b8</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cdd88a05bdf3bdd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer - Onsite Interviews (Denver)</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, Azure, Data Factory, Event Hubs, Zookeeper, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb35aa20ed18f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Anywhere Real Estate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist I &amp; II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Senior IT Analyst - Data Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PHP Web Application Developer (Modernization)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EBG</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42f3c1cc306e46b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PHP Web Application Developer (Modernization)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EBG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d17ef03868a4db</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PHP Web Application Developer (Modernization)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EBG</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2f5b1a7f332d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anywhere Real Estate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfe24311f764a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cyber Security Design Sr Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP APME Architect (Agent Performance Management)</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emcube Technlogy</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dc9a778272d57a</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, IAM, Hadoop, Hive, Spark, Scala, Kafka, ETL, MLflow, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocMe360</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b261e4efaa78a896</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DocMe360</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324a9abb3a15c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cyber Security Design Sr Specialist</t>
+          <t>Senior DevOps Engineer (Azure DevOps)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Smart IMS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464717bcd30ad3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Elixir Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Ojai, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,207 +1441,207 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,207 +1651,207 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40465efa7f1818bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Modeler</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Popular, Inc.</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0d552643e7eedb</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Enterprise Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Engineer, Enterprise Data Management</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Delaware North</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2653ae0372ac3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Remote</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Power BI</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2a58090f4bb497</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=d903df923be7974b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud/Software Architect - 100% Remote Opportunity</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4f0e576986052</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,264 +2386,264 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97d5c07dca33568</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,81 +2652,81 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Machine Learning Engineer II - AI Research</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d903df923be7974b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,1162 +2736,147 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b788ca36aaa4f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Plante Moran</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Southfield, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technical Architect</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Clarivate</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c2a638eb5531d44</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technical Architect</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Clarivate</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6322cffeb20c3419</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technical Architect</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Clarivate</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=051ff6a58134edd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>JavaScript (ES6), Node.js, React, AWS, Lambda Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>The Consortium Inc.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, DynamoDB, NoSQL, CI/CD, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41ccf0c820aa8964</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Waséyabek Development Company</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Otsego, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Sr Business Data Analyst</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sr Python Developer - Onsite - Atlanta GA</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>M-TECH SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Dunwoody, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b195bf8b57adc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Full Stack Developer Intern</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Westford, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>The Clearing House Payments Company</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Liberty, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Gong</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Quality Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Circle.so</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II - AI Research</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II - AI Research</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II - AI Research</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>The New IEM, LLC</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07073f5e67bf6929</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Nexxen</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1c6fb0f0eba666</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Salesforce AI / Einstein Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, MLOps, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack – Python, React, Azure)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96ebd296c9a36070</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Full Stack Java Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Southlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, CI/CD, Jenkins, Jenkins, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58ddcb632ed49aa5</t>
         </is>
       </c>
     </row>
